--- a/Chennai-March-2026.xlsx
+++ b/Chennai-March-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="50">
   <si>
     <t>Sr. No</t>
   </si>
@@ -142,16 +142,13 @@
     <t>TN14AK9389</t>
   </si>
   <si>
-    <t>DZIRE CNG</t>
-  </si>
-  <si>
     <t>DZIRE</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Citron</t>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>30/05/2023</t>
@@ -708,7 +705,7 @@
         <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" s="2">
         <v>46003</v>
@@ -788,10 +785,10 @@
         <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H4">
         <v>47673</v>
@@ -868,7 +865,7 @@
         <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G5" s="2">
         <v>44815</v>
@@ -948,7 +945,7 @@
         <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2">
         <v>44815</v>
@@ -1028,7 +1025,7 @@
         <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G7" s="2">
         <v>44815</v>
@@ -1108,10 +1105,10 @@
         <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H8">
         <v>139559</v>
@@ -1188,7 +1185,7 @@
         <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G9" s="2">
         <v>44659</v>
@@ -1268,10 +1265,10 @@
         <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H10">
         <v>125588</v>
@@ -1348,10 +1345,10 @@
         <v>37</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H11">
         <v>80078</v>
@@ -1428,7 +1425,7 @@
         <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G12" s="2">
         <v>45142</v>
@@ -1508,7 +1505,7 @@
         <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G13" s="2">
         <v>44628</v>
@@ -1588,7 +1585,7 @@
         <v>40</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G14" s="2">
         <v>44628</v>
@@ -1668,10 +1665,10 @@
         <v>41</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H15">
         <v>35070</v>
